--- a/InputData/elec/SES/Seasonal Electricity Storage.xlsx
+++ b/InputData/elec/SES/Seasonal Electricity Storage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\elec\SES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\SES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017C1B14-8274-4182-9C89-7F44E6BEEFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8676F0C9-F8F7-4386-B01C-5F726BE2AEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29790" yWindow="2370" windowWidth="29460" windowHeight="20220" xr2:uid="{78AD1A57-EE8B-429E-82B5-7F18B2E9410A}"/>
+    <workbookView xWindow="30030" yWindow="2355" windowWidth="19200" windowHeight="11205" activeTab="4" xr2:uid="{78AD1A57-EE8B-429E-82B5-7F18B2E9410A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -250,7 +250,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -262,7 +262,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -339,9 +338,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -379,7 +378,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -485,7 +484,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -627,7 +626,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -636,28 +635,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854D2354-DEF2-427F-84E2-87F1715F500F}">
   <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="65.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="65.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -665,170 +664,164 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="3">
         <v>2023</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B9" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B19" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B23" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="9"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="8"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="9"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="8"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -847,9 +840,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC25C513-BECB-45B3-B494-6104E16AFED7}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -857,13 +850,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>40</v>
       </c>
     </row>
@@ -878,108 +871,111 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.5703125" customWidth="1"/>
+    <col min="1" max="1" width="40.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="2">
+        <v>2020</v>
+      </c>
+      <c r="C1">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -987,15 +983,14 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <f>$B2</f>
         <v>100</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:AE2" si="0">$B2</f>
+        <f>$C2</f>
         <v>100</v>
       </c>
       <c r="E2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E2:AF2" si="0">$C2</f>
         <v>100</v>
       </c>
       <c r="F2">
@@ -1099,6 +1094,10 @@
         <v>100</v>
       </c>
       <c r="AE2">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="AF2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -1114,13 +1113,13 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.54296875" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
@@ -1128,7 +1127,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1147,13 +1146,13 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="40.54296875" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
@@ -1161,7 +1160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1175,6 +1174,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -1318,29 +1332,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95130481-93A7-4799-92DC-29B3D1E9AA27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49D39F3A-C48D-49B7-9F00-EA79084F2811}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA97C5A4-7DD2-48B5-8097-300A9EF6D7A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA97C5A4-7DD2-48B5-8097-300A9EF6D7A4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49D39F3A-C48D-49B7-9F00-EA79084F2811}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95130481-93A7-4799-92DC-29B3D1E9AA27}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>